--- a/data/trans_camb/POLIPATOLOGIA_2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,66</t>
+          <t>2,38; 11,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 8,63</t>
+          <t>-0,09; 8,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 22,49</t>
+          <t>12,91; 22,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 18,54</t>
+          <t>8,56; 18,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,95</t>
+          <t>3,04; 13,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 19,99</t>
+          <t>5,75; 20,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 13,45</t>
+          <t>6,9; 13,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,55</t>
+          <t>2,95; 9,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 20,52</t>
+          <t>12,17; 20,56</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,02; 69,45</t>
+          <t>9,91; 65,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 51,97</t>
+          <t>-0,85; 50,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,01; 137,57</t>
+          <t>59,93; 133,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,16; 67,43</t>
+          <t>26,33; 68,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 47,5</t>
+          <t>9,77; 48,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 72,93</t>
+          <t>18,81; 73,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,56; 59,03</t>
+          <t>26,16; 61,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 42,49</t>
+          <t>11,21; 43,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,37; 89,57</t>
+          <t>47,75; 89,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 7,95</t>
+          <t>-0,4; 7,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 7,04</t>
+          <t>-0,42; 7,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 10,15</t>
+          <t>-10,9; 9,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 8,62</t>
+          <t>-0,59; 8,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,8</t>
+          <t>-1,07; 7,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 15,04</t>
+          <t>6,85; 15,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,98</t>
+          <t>1,34; 7,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,04</t>
+          <t>0,54; 6,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 10,7</t>
+          <t>-5,53; 10,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 44,93</t>
+          <t>-1,65; 41,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 39,15</t>
+          <t>-2,09; 39,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 52,04</t>
+          <t>-50,08; 51,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 27,04</t>
+          <t>-1,4; 26,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 24,81</t>
+          <t>-2,97; 25,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,42; 47,35</t>
+          <t>19,23; 48,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 26,83</t>
+          <t>4,98; 28,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 23,44</t>
+          <t>1,92; 23,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 40,37</t>
+          <t>-19,65; 41,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 5,84</t>
+          <t>-3,02; 6,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,62</t>
+          <t>-2,22; 6,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 17,71</t>
+          <t>7,71; 17,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,05</t>
+          <t>-7,73; 2,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -0,95</t>
+          <t>-10,85; -1,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 39,9</t>
+          <t>3,99; 41,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,72</t>
+          <t>-3,64; 3,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,61</t>
+          <t>-5,25; 1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 35,17</t>
+          <t>8,33; 34,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 32,89</t>
+          <t>-13,89; 34,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 37,09</t>
+          <t>-10,38; 39,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,19; 100,02</t>
+          <t>34,89; 101,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 6,03</t>
+          <t>-19,34; 7,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,55; -2,61</t>
+          <t>-27,24; -2,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,24; 114,63</t>
+          <t>11,03; 120,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 10,14</t>
+          <t>-12,07; 11,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 6,05</t>
+          <t>-18,0; 4,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,94; 126,89</t>
+          <t>28,57; 125,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,73</t>
+          <t>1,74; 9,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,16</t>
+          <t>2,26; 10,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,1; 18,28</t>
+          <t>10,34; 18,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,51</t>
+          <t>1,86; 10,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 8,61</t>
+          <t>-0,15; 8,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 27,64</t>
+          <t>12,28; 26,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,54</t>
+          <t>3,1; 9,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,38</t>
+          <t>2,35; 8,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,38; 22,65</t>
+          <t>12,8; 23,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,86; 53,35</t>
+          <t>8,07; 52,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,8; 54,89</t>
+          <t>10,17; 54,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,24; 99,85</t>
+          <t>45,99; 99,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 34,43</t>
+          <t>5,16; 33,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 27,74</t>
+          <t>-0,47; 27,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,56; 86,96</t>
+          <t>34,68; 83,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,22; 33,87</t>
+          <t>10,97; 35,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 32,62</t>
+          <t>8,35; 32,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43,33; 85,06</t>
+          <t>45,8; 86,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,68</t>
+          <t>2,64; 6,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,16</t>
+          <t>2,02; 6,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,45; 13,78</t>
+          <t>3,88; 13,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,54</t>
+          <t>2,91; 7,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,86</t>
+          <t>0,25; 5,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,28; 25,1</t>
+          <t>11,53; 24,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,41</t>
+          <t>3,3; 6,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,84</t>
+          <t>1,79; 4,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 19,1</t>
+          <t>9,49; 18,67</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11,93; 35,01</t>
+          <t>12,67; 34,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10,27; 32,93</t>
+          <t>9,85; 32,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23,42; 71,63</t>
+          <t>20,0; 71,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,1; 23,37</t>
+          <t>8,22; 23,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,5; 15,04</t>
+          <t>0,73; 16,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,79; 74,1</t>
+          <t>34,13; 75,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,51; 24,46</t>
+          <t>11,99; 24,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,54; 18,65</t>
+          <t>6,39; 18,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,07; 71,72</t>
+          <t>35,35; 70,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,04</t>
+          <t>17,65</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,85</t>
+          <t>17,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 11,28</t>
+          <t>2,37; 11,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 8,46</t>
+          <t>-0,11; 8,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 22,82</t>
+          <t>12,82; 22,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 18,66</t>
+          <t>8,26; 18,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 13,38</t>
+          <t>3,03; 12,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 20,16</t>
+          <t>12,83; 22,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,86</t>
+          <t>6,94; 13,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,69</t>
+          <t>3,14; 9,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,17; 20,56</t>
+          <t>14,67; 21,43</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 65,19</t>
+          <t>11,82; 66,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 50,8</t>
+          <t>0,25; 53,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,93; 133,28</t>
+          <t>61,84; 134,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,33; 68,21</t>
+          <t>25,28; 65,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,77; 48,74</t>
+          <t>9,28; 47,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 73,14</t>
+          <t>39,2; 81,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,16; 61,1</t>
+          <t>26,85; 59,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 43,06</t>
+          <t>11,86; 42,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,75; 89,96</t>
+          <t>55,5; 94,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>10,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>9,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 7,39</t>
+          <t>0,01; 7,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,06</t>
+          <t>-0,65; 6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 9,83</t>
+          <t>4,67; 12,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,35</t>
+          <t>-0,75; 8,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,9</t>
+          <t>-0,81; 8,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 15,22</t>
+          <t>6,85; 14,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,14</t>
+          <t>1,14; 7,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,04</t>
+          <t>0,62; 6,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 10,84</t>
+          <t>6,9; 12,83</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 41,12</t>
+          <t>-0,36; 41,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 39,31</t>
+          <t>-2,9; 37,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 51,21</t>
+          <t>21,21; 68,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 26,48</t>
+          <t>-1,92; 26,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 25,04</t>
+          <t>-2,29; 25,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,23; 48,89</t>
+          <t>18,72; 46,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 28,72</t>
+          <t>4,09; 27,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 23,52</t>
+          <t>2,01; 25,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 41,22</t>
+          <t>23,84; 50,33</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,7</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,88</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,39</t>
+          <t>10,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,27</t>
+          <t>-3,2; 5,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,99</t>
+          <t>-2,16; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 17,77</t>
+          <t>7,7; 16,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,36</t>
+          <t>-8,05; 2,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -1,05</t>
+          <t>-10,92; -0,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 41,37</t>
+          <t>3,91; 13,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,12</t>
+          <t>-4,02; 2,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 1,39</t>
+          <t>-5,39; 1,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 34,83</t>
+          <t>6,95; 13,84</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 34,72</t>
+          <t>-14,79; 32,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 39,1</t>
+          <t>-9,63; 33,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,89; 101,62</t>
+          <t>33,73; 93,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 7,18</t>
+          <t>-19,89; 6,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,24; -2,79</t>
+          <t>-27,74; -2,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 120,51</t>
+          <t>9,82; 40,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 11,62</t>
+          <t>-13,02; 9,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 4,97</t>
+          <t>-17,36; 6,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,57; 125,48</t>
+          <t>23,68; 52,26</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>13,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,32</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,04</t>
+          <t>13,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,47</t>
+          <t>1,87; 9,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 10,01</t>
+          <t>2,41; 9,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,23</t>
+          <t>9,04; 16,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 10,39</t>
+          <t>1,44; 10,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 8,57</t>
+          <t>-0,01; 8,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,28; 26,9</t>
+          <t>9,54; 17,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,11</t>
+          <t>3,3; 9,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,24</t>
+          <t>2,35; 7,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,44</t>
+          <t>10,66; 16,16</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,07; 52,83</t>
+          <t>7,91; 50,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,17; 54,0</t>
+          <t>11,08; 55,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,99; 99,0</t>
+          <t>41,28; 91,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 33,87</t>
+          <t>4,16; 32,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 27,15</t>
+          <t>-0,17; 26,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,68; 83,24</t>
+          <t>27,11; 56,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,97; 35,67</t>
+          <t>11,49; 34,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 32,14</t>
+          <t>8,01; 31,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45,8; 86,94</t>
+          <t>37,41; 63,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,71</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,84</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>12,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,46</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,1</t>
+          <t>2,04; 6,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,74</t>
+          <t>10,31; 14,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,78</t>
+          <t>2,85; 7,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,14</t>
+          <t>0,1; 4,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,53; 24,7</t>
+          <t>10,43; 14,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,48</t>
+          <t>3,24; 6,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,91</t>
+          <t>1,91; 4,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 18,67</t>
+          <t>10,98; 14,26</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,67; 34,49</t>
+          <t>10,63; 34,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9,85; 32,38</t>
+          <t>9,23; 32,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,0; 71,67</t>
+          <t>49,57; 79,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,22; 23,97</t>
+          <t>8,34; 23,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,73; 16,32</t>
+          <t>0,22; 15,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,13; 75,17</t>
+          <t>29,65; 45,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,99; 24,96</t>
+          <t>11,78; 24,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,39; 18,83</t>
+          <t>6,93; 19,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,35; 70,05</t>
+          <t>40,05; 55,09</t>
         </is>
       </c>
     </row>
